--- a/Data/Datasets/Output/meta_feature_training_stats_.xlsx
+++ b/Data/Datasets/Output/meta_feature_training_stats_.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/38498c2a7fab902e/tuks/master/code/Thesis/Data/Datasets/Output/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/38498c2a7fab902e/tuks/master/code/Laptop/Data/Datasets/Output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="173" documentId="11_F25DC773A252ABDACC1048A2915872405ADE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF60EAB1-CDB3-450E-AB17-AE7C82F601B0}"/>
+  <xr:revisionPtr revIDLastSave="178" documentId="11_F25DC773A252ABDACC1048A2915872405ADE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{750D6146-BAE7-49C0-87BF-7D43537F1862}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -151,7 +151,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -163,6 +163,21 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -255,7 +270,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -282,6 +297,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -980,7 +998,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37982CAE-0D25-43BC-94BB-81C8EE4EF796}">
-  <dimension ref="B2:I16"/>
+  <dimension ref="B2:I12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="31" bestFit="1" customWidth="1"/>
@@ -1140,28 +1158,28 @@
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="13">
         <v>5.8151260504201598</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="14">
         <v>1</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="13">
         <v>0.84033613445378097</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="14">
         <v>64</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="13">
         <v>53.781512605042003</v>
       </c>
-      <c r="H8" s="1">
+      <c r="H8" s="14">
         <v>136</v>
       </c>
-      <c r="I8" s="4">
+      <c r="I8" s="13">
         <f>H8/255*100</f>
         <v>53.333333333333336</v>
       </c>
@@ -1194,28 +1212,28 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="13">
         <v>5.3176470588235203</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" s="14">
         <v>2</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="13">
         <v>0.78431372549019596</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10" s="14">
         <v>63</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G10" s="13">
         <v>24.705882352941099</v>
       </c>
-      <c r="H10" s="1">
-        <v>0</v>
-      </c>
-      <c r="I10" s="4">
+      <c r="H10" s="14">
+        <v>0</v>
+      </c>
+      <c r="I10" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1248,36 +1266,30 @@
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="13">
         <v>4.9215686274509798</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" s="14">
         <v>34</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="13">
         <v>13.3333333333333</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12" s="14">
         <v>115</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G12" s="13">
         <v>45.0980392156862</v>
       </c>
-      <c r="H12" s="1">
-        <v>0</v>
-      </c>
-      <c r="I12" s="4">
+      <c r="H12" s="14">
+        <v>0</v>
+      </c>
+      <c r="I12" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="E16">
-        <f>255-136</f>
-        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -1289,5 +1301,6 @@
     <mergeCell ref="F2:G2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Data/Datasets/Output/meta_feature_training_stats_.xlsx
+++ b/Data/Datasets/Output/meta_feature_training_stats_.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/38498c2a7fab902e/tuks/master/code/Laptop/Data/Datasets/Output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="178" documentId="11_F25DC773A252ABDACC1048A2915872405ADE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{750D6146-BAE7-49C0-87BF-7D43537F1862}"/>
+  <xr:revisionPtr revIDLastSave="210" documentId="11_F25DC773A252ABDACC1048A2915872405ADE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A65EF0BF-920C-41FD-8F43-027CAF5CCB53}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="37">
   <si>
     <t>count</t>
   </si>
@@ -63,36 +63,6 @@
     <t>75%</t>
   </si>
   <si>
-    <t>times the technique can’t be used</t>
-  </si>
-  <si>
-    <t>average rank</t>
-  </si>
-  <si>
-    <t>baseline testing loss</t>
-  </si>
-  <si>
-    <t>batch normalisation testing loss</t>
-  </si>
-  <si>
-    <t>dropout testing loss</t>
-  </si>
-  <si>
-    <t>layer normalisation testing loss</t>
-  </si>
-  <si>
-    <t>prune testing loss</t>
-  </si>
-  <si>
-    <t>weight decay testing loss</t>
-  </si>
-  <si>
-    <t>weight normalisation testing loss</t>
-  </si>
-  <si>
-    <t>weight perturbation testing loss</t>
-  </si>
-  <si>
     <t>number of features</t>
   </si>
   <si>
@@ -132,16 +102,52 @@
     <t>noise to signal ratio of features</t>
   </si>
   <si>
-    <t>percent(%)</t>
-  </si>
-  <si>
-    <t>times the technique resulted in the best perfromes</t>
-  </si>
-  <si>
-    <t>times the technique resulted in the worst perfromes</t>
-  </si>
-  <si>
-    <t>SMOTE testing loss *</t>
+    <t>Average rank</t>
+  </si>
+  <si>
+    <t>Number of times the technique is the best</t>
+  </si>
+  <si>
+    <t>Number of times the technique is the worst</t>
+  </si>
+  <si>
+    <t>Times the technique can’t be used</t>
+  </si>
+  <si>
+    <t>Baseline</t>
+  </si>
+  <si>
+    <t>Batch normalisation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMOTE </t>
+  </si>
+  <si>
+    <t>Techinques</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Percent(%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dropout </t>
+  </si>
+  <si>
+    <t>Layer normalisation</t>
+  </si>
+  <si>
+    <t>Prune</t>
+  </si>
+  <si>
+    <t>Weight decay</t>
+  </si>
+  <si>
+    <t>Weight normalisation</t>
+  </si>
+  <si>
+    <t>Weight perturbation</t>
   </si>
 </sst>
 </file>
@@ -270,20 +276,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -297,9 +300,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -315,6 +318,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -616,7 +623,7 @@
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1">
         <v>255</v>
@@ -645,7 +652,7 @@
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C4" s="1">
         <v>255</v>
@@ -674,7 +681,7 @@
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C5" s="1">
         <v>255</v>
@@ -703,7 +710,7 @@
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C6" s="1">
         <v>255</v>
@@ -732,7 +739,7 @@
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C7" s="1">
         <v>255</v>
@@ -761,7 +768,7 @@
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C8" s="1">
         <v>255</v>
@@ -790,7 +797,7 @@
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C9" s="1">
         <v>255</v>
@@ -819,7 +826,7 @@
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C10" s="1">
         <v>255</v>
@@ -848,7 +855,7 @@
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C11" s="1">
         <v>255</v>
@@ -877,7 +884,7 @@
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="C12" s="1">
         <v>255</v>
@@ -906,7 +913,7 @@
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C13" s="1">
         <v>255</v>
@@ -935,7 +942,7 @@
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="C14" s="1">
         <v>255</v>
@@ -964,7 +971,7 @@
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C15" s="1">
         <v>255</v>
@@ -1001,7 +1008,7 @@
   <dimension ref="B2:I12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="31" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
@@ -1010,48 +1017,50 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6"/>
-      <c r="C2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="E2" s="11"/>
-      <c r="F2" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="G2" s="11"/>
-      <c r="H2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="5"/>
+      <c r="B2" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="12"/>
+      <c r="F2" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="12"/>
+      <c r="H2" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" s="8"/>
     </row>
     <row r="3" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="7"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>31</v>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" s="13" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C4" s="4">
         <v>2.5137254901960699</v>
@@ -1078,7 +1087,7 @@
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C5" s="4">
         <v>2.3843137254901898</v>
@@ -1105,7 +1114,7 @@
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="C6" s="4">
         <v>2.37254901960784</v>
@@ -1132,7 +1141,7 @@
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="C7" s="4">
         <v>3.42745098039215</v>
@@ -1158,35 +1167,35 @@
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="13">
+      <c r="B8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="6">
         <v>5.8151260504201598</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="7">
         <v>1</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="6">
         <v>0.84033613445378097</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="7">
         <v>64</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="6">
         <v>53.781512605042003</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="7">
         <v>136</v>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="6">
         <f>H8/255*100</f>
         <v>53.333333333333336</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C9" s="4">
         <v>2.7254901960784301</v>
@@ -1212,35 +1221,35 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B10" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="13">
+      <c r="B10" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="6">
         <v>5.3176470588235203</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="7">
         <v>2</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="6">
         <v>0.78431372549019596</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="7">
         <v>63</v>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="6">
         <v>24.705882352941099</v>
       </c>
-      <c r="H10" s="14">
-        <v>0</v>
-      </c>
-      <c r="I10" s="13">
+      <c r="H10" s="7">
+        <v>0</v>
+      </c>
+      <c r="I10" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="C11" s="4">
         <v>2.4196078431372499</v>
@@ -1266,28 +1275,28 @@
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B12" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="13">
+      <c r="B12" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="6">
         <v>4.9215686274509798</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="7">
         <v>34</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="6">
         <v>13.3333333333333</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F12" s="7">
         <v>115</v>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="6">
         <v>45.0980392156862</v>
       </c>
-      <c r="H12" s="14">
-        <v>0</v>
-      </c>
-      <c r="I12" s="13">
+      <c r="H12" s="7">
+        <v>0</v>
+      </c>
+      <c r="I12" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
